--- a/Example/OysterReport.ExcelToPdfSample/seikyusyo.xlsx
+++ b/Example/OysterReport.ExcelToPdfSample/seikyusyo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\OysterReport.ExcelToPdfSample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57F159-FFA6-4B32-89A6-E4BD17FAC35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8B07C-EE18-442C-BCFD-1BA09684269D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50760" yWindow="3330" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40050" yWindow="1665" windowWidth="21480" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -761,13 +761,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>135957</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>72473</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>1667319</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>46828</xdr:rowOff>
@@ -811,13 +811,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>19399</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>55144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>2095499</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -835,7 +835,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3915124" y="2407819"/>
+          <a:off x="3715099" y="2407819"/>
           <a:ext cx="2076100" cy="640181"/>
           <a:chOff x="3962400" y="2381250"/>
           <a:chExt cx="1885950" cy="628650"/>
@@ -1014,13 +1014,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>1381125</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>2101125</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>138975</xdr:rowOff>
@@ -1085,8 +1085,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル" displayName="テーブル" ref="B21:F46" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6">
-  <autoFilter ref="B21:F46" xr:uid="{00000000-0009-0000-0100-000009000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="テーブル" displayName="テーブル" ref="A21:E46" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6">
+  <autoFilter ref="A21:E46" xr:uid="{00000000-0009-0000-0100-000009000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1099,7 +1099,7 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="数量" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="単価" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="金額" dataDxfId="0">
-      <calculatedColumnFormula>D22*E22</calculatedColumnFormula>
+      <calculatedColumnFormula>C22*D22</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1369,532 +1369,531 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:F60"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-    </row>
-    <row r="2" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="F3" s="6" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="F4" s="7" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" spans="2:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="34" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="2:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="34"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
       <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="36"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="F10" s="5" t="s">
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="35"/>
       <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B12" s="36"/>
       <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="B13" s="40"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="35"/>
       <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="35"/>
       <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
         <v>18</v>
       </c>
+      <c r="B16" s="35"/>
       <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-    </row>
-    <row r="18" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="37">
-        <f>F49</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="41" t="s">
+      <c r="B18" s="37">
+        <f>E49</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="39"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="42"/>
-    </row>
-    <row r="20" spans="2:6" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="25" t="s">
+    <row r="19" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="42"/>
+    </row>
+    <row r="20" spans="1:5" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
         <v>8</v>
       </c>
+      <c r="B21" s="26" t="s">
+        <v>19</v>
+      </c>
       <c r="C21" s="26" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="19">
-        <f t="shared" ref="F22:F46" si="0">D22*E22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="11"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="19">
+        <f t="shared" ref="E22:E46" si="0">C22*D22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="11"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="11"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
       <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
       <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="12"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="11"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="11"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12"/>
       <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="11"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
       <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
       <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="11"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="15"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="15"/>
+      <c r="B46" s="16"/>
       <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="23"/>
+      <c r="E46" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="13" t="s">
+      <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="21">
-        <f>SUM(F22:F46)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="21">
+        <f>SUM(E22:E46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="27" t="s">
+      <c r="D48" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="28">
-        <f>F47*0.1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E48" s="28">
+        <f>E47*0.1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="13" t="s">
+      <c r="D49" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="14">
-        <f>SUM(F47:F48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="29" t="s">
+      <c r="E49" s="14">
+        <f>SUM(E47:E48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
         <v>20</v>
       </c>
+      <c r="B50" s="29"/>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
       <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-    </row>
-    <row r="51" spans="2:6" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:5" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="30"/>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
       <c r="D51" s="30"/>
       <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="30"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="30"/>
       <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31"/>
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="31"/>
       <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-    </row>
-    <row r="55" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="32"/>
       <c r="B55" s="32"/>
       <c r="C55" s="32"/>
       <c r="D55" s="32"/>
       <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-    </row>
-    <row r="56" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="32"/>
       <c r="B56" s="32"/>
       <c r="C56" s="32"/>
       <c r="D56" s="32"/>
       <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-    </row>
-    <row r="57" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="32"/>
       <c r="B57" s="32"/>
       <c r="C57" s="32"/>
       <c r="D57" s="32"/>
       <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-    </row>
-    <row r="58" spans="2:6" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="33"/>
       <c r="B58" s="33"/>
       <c r="C58" s="33"/>
       <c r="D58" s="33"/>
       <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
       <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F54"/>
-    <mergeCell ref="B55:F58"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A51:E54"/>
+    <mergeCell ref="A55:E58"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="D18:D19"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
